--- a/artfynd/A 10282-2024 artfynd.xlsx
+++ b/artfynd/A 10282-2024 artfynd.xlsx
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124466782</v>
+        <v>124466729</v>
       </c>
       <c r="B4" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>454914</v>
+        <v>454901</v>
       </c>
       <c r="R4" t="n">
-        <v>6791574</v>
+        <v>6791638</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1088,7 +1088,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124466768</v>
+        <v>124466783</v>
       </c>
       <c r="B6" t="n">
         <v>78810</v>
@@ -1128,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>454929</v>
+        <v>454911</v>
       </c>
       <c r="R6" t="n">
-        <v>6791494</v>
+        <v>6791571</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1190,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124466729</v>
+        <v>124466762</v>
       </c>
       <c r="B7" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1202,38 +1202,47 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>454901</v>
+        <v>454907</v>
       </c>
       <c r="R7" t="n">
-        <v>6791638</v>
+        <v>6791625</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1292,10 +1301,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124466711</v>
+        <v>124466782</v>
       </c>
       <c r="B8" t="n">
-        <v>78842</v>
+        <v>78810</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1308,21 +1317,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1332,10 +1341,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>454951</v>
+        <v>454914</v>
       </c>
       <c r="R8" t="n">
-        <v>6791471</v>
+        <v>6791574</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1394,7 +1403,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124466767</v>
+        <v>124466779</v>
       </c>
       <c r="B9" t="n">
         <v>78810</v>
@@ -1434,10 +1443,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>454933</v>
+        <v>454886</v>
       </c>
       <c r="R9" t="n">
-        <v>6791499</v>
+        <v>6791653</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1496,10 +1505,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124466779</v>
+        <v>124466759</v>
       </c>
       <c r="B10" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1508,38 +1517,47 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>454886</v>
+        <v>454956</v>
       </c>
       <c r="R10" t="n">
-        <v>6791653</v>
+        <v>6791469</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1598,10 +1616,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124466766</v>
+        <v>124466750</v>
       </c>
       <c r="B11" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1610,38 +1628,47 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>454930</v>
+        <v>454893</v>
       </c>
       <c r="R11" t="n">
-        <v>6791516</v>
+        <v>6791627</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1700,10 +1727,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124466762</v>
+        <v>124466769</v>
       </c>
       <c r="B12" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1712,47 +1739,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>454907</v>
+        <v>454970</v>
       </c>
       <c r="R12" t="n">
-        <v>6791625</v>
+        <v>6791393</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1811,7 +1829,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124466769</v>
+        <v>124466767</v>
       </c>
       <c r="B13" t="n">
         <v>78810</v>
@@ -1851,10 +1869,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>454970</v>
+        <v>454933</v>
       </c>
       <c r="R13" t="n">
-        <v>6791393</v>
+        <v>6791499</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1913,10 +1931,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124466759</v>
+        <v>124466766</v>
       </c>
       <c r="B14" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1925,47 +1943,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>454956</v>
+        <v>454930</v>
       </c>
       <c r="R14" t="n">
-        <v>6791469</v>
+        <v>6791516</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2024,10 +2033,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124466750</v>
+        <v>124466711</v>
       </c>
       <c r="B15" t="n">
-        <v>98101</v>
+        <v>78842</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2036,47 +2045,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>454893</v>
+        <v>454951</v>
       </c>
       <c r="R15" t="n">
-        <v>6791627</v>
+        <v>6791471</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2135,10 +2135,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124466783</v>
+        <v>124466714</v>
       </c>
       <c r="B16" t="n">
-        <v>78810</v>
+        <v>90977</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2147,25 +2147,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2175,10 +2175,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>454911</v>
+        <v>454969</v>
       </c>
       <c r="R16" t="n">
-        <v>6791571</v>
+        <v>6791399</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2237,10 +2237,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124466714</v>
+        <v>124466768</v>
       </c>
       <c r="B17" t="n">
-        <v>90977</v>
+        <v>78810</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2249,25 +2249,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2277,10 +2277,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>454969</v>
+        <v>454929</v>
       </c>
       <c r="R17" t="n">
-        <v>6791399</v>
+        <v>6791494</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>

--- a/artfynd/A 10282-2024 artfynd.xlsx
+++ b/artfynd/A 10282-2024 artfynd.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124466712</v>
+        <v>124466783</v>
       </c>
       <c r="B3" t="n">
-        <v>78842</v>
+        <v>78810</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>454964</v>
+        <v>454911</v>
       </c>
       <c r="R3" t="n">
-        <v>6791409</v>
+        <v>6791571</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -986,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124466710</v>
+        <v>124466759</v>
       </c>
       <c r="B5" t="n">
-        <v>78842</v>
+        <v>98101</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -998,38 +998,47 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>454946</v>
+        <v>454956</v>
       </c>
       <c r="R5" t="n">
-        <v>6791477</v>
+        <v>6791469</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,10 +1097,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124466783</v>
+        <v>124466750</v>
       </c>
       <c r="B6" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1100,38 +1109,47 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>454911</v>
+        <v>454893</v>
       </c>
       <c r="R6" t="n">
-        <v>6791571</v>
+        <v>6791627</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1190,10 +1208,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124466762</v>
+        <v>124466767</v>
       </c>
       <c r="B7" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1202,47 +1220,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>454907</v>
+        <v>454933</v>
       </c>
       <c r="R7" t="n">
-        <v>6791625</v>
+        <v>6791499</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1301,7 +1310,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124466782</v>
+        <v>124466768</v>
       </c>
       <c r="B8" t="n">
         <v>78810</v>
@@ -1341,10 +1350,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>454914</v>
+        <v>454929</v>
       </c>
       <c r="R8" t="n">
-        <v>6791574</v>
+        <v>6791494</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1403,10 +1412,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124466779</v>
+        <v>124466762</v>
       </c>
       <c r="B9" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1415,38 +1424,47 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>454886</v>
+        <v>454907</v>
       </c>
       <c r="R9" t="n">
-        <v>6791653</v>
+        <v>6791625</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1505,10 +1523,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124466759</v>
+        <v>124466710</v>
       </c>
       <c r="B10" t="n">
-        <v>98101</v>
+        <v>78842</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1517,47 +1535,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>454956</v>
+        <v>454946</v>
       </c>
       <c r="R10" t="n">
-        <v>6791469</v>
+        <v>6791477</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1616,10 +1625,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124466750</v>
+        <v>124466711</v>
       </c>
       <c r="B11" t="n">
-        <v>98101</v>
+        <v>78842</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1628,47 +1637,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>454893</v>
+        <v>454951</v>
       </c>
       <c r="R11" t="n">
-        <v>6791627</v>
+        <v>6791471</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1727,10 +1727,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124466769</v>
+        <v>124466712</v>
       </c>
       <c r="B12" t="n">
-        <v>78810</v>
+        <v>78842</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1743,21 +1743,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1767,10 +1767,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>454970</v>
+        <v>454964</v>
       </c>
       <c r="R12" t="n">
-        <v>6791393</v>
+        <v>6791409</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1829,7 +1829,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124466767</v>
+        <v>124466782</v>
       </c>
       <c r="B13" t="n">
         <v>78810</v>
@@ -1869,10 +1869,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>454933</v>
+        <v>454914</v>
       </c>
       <c r="R13" t="n">
-        <v>6791499</v>
+        <v>6791574</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2033,10 +2033,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124466711</v>
+        <v>124466714</v>
       </c>
       <c r="B15" t="n">
-        <v>78842</v>
+        <v>90977</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2045,25 +2045,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>185</v>
+        <v>5447</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2073,10 +2073,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>454951</v>
+        <v>454969</v>
       </c>
       <c r="R15" t="n">
-        <v>6791471</v>
+        <v>6791399</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2135,10 +2135,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124466714</v>
+        <v>124466779</v>
       </c>
       <c r="B16" t="n">
-        <v>90977</v>
+        <v>78810</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2147,25 +2147,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2175,10 +2175,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>454969</v>
+        <v>454886</v>
       </c>
       <c r="R16" t="n">
-        <v>6791399</v>
+        <v>6791653</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2237,7 +2237,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124466768</v>
+        <v>124466769</v>
       </c>
       <c r="B17" t="n">
         <v>78810</v>
@@ -2277,10 +2277,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>454929</v>
+        <v>454970</v>
       </c>
       <c r="R17" t="n">
-        <v>6791494</v>
+        <v>6791393</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>

--- a/artfynd/A 10282-2024 artfynd.xlsx
+++ b/artfynd/A 10282-2024 artfynd.xlsx
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124466783</v>
+        <v>124466769</v>
       </c>
       <c r="B3" t="n">
         <v>78810</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>454911</v>
+        <v>454970</v>
       </c>
       <c r="R3" t="n">
-        <v>6791571</v>
+        <v>6791393</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124466729</v>
+        <v>124466766</v>
       </c>
       <c r="B4" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>454901</v>
+        <v>454930</v>
       </c>
       <c r="R4" t="n">
-        <v>6791638</v>
+        <v>6791516</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124466759</v>
+        <v>124466782</v>
       </c>
       <c r="B5" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -998,47 +998,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>454956</v>
+        <v>454914</v>
       </c>
       <c r="R5" t="n">
-        <v>6791469</v>
+        <v>6791574</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1097,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124466750</v>
+        <v>124466779</v>
       </c>
       <c r="B6" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1109,47 +1100,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>454893</v>
+        <v>454886</v>
       </c>
       <c r="R6" t="n">
-        <v>6791627</v>
+        <v>6791653</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1310,10 +1292,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124466768</v>
+        <v>124466759</v>
       </c>
       <c r="B8" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1322,38 +1304,47 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>454929</v>
+        <v>454956</v>
       </c>
       <c r="R8" t="n">
-        <v>6791494</v>
+        <v>6791469</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1412,10 +1403,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124466762</v>
+        <v>124466714</v>
       </c>
       <c r="B9" t="n">
-        <v>98101</v>
+        <v>90977</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1424,47 +1415,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>454907</v>
+        <v>454969</v>
       </c>
       <c r="R9" t="n">
-        <v>6791625</v>
+        <v>6791399</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1523,10 +1505,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124466710</v>
+        <v>124466762</v>
       </c>
       <c r="B10" t="n">
-        <v>78842</v>
+        <v>98101</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1535,38 +1517,47 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>454946</v>
+        <v>454907</v>
       </c>
       <c r="R10" t="n">
-        <v>6791477</v>
+        <v>6791625</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1625,7 +1616,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124466711</v>
+        <v>124466712</v>
       </c>
       <c r="B11" t="n">
         <v>78842</v>
@@ -1665,10 +1656,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>454951</v>
+        <v>454964</v>
       </c>
       <c r="R11" t="n">
-        <v>6791471</v>
+        <v>6791409</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1727,10 +1718,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124466712</v>
+        <v>124466783</v>
       </c>
       <c r="B12" t="n">
-        <v>78842</v>
+        <v>78810</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1743,21 +1734,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1767,10 +1758,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>454964</v>
+        <v>454911</v>
       </c>
       <c r="R12" t="n">
-        <v>6791409</v>
+        <v>6791571</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1829,10 +1820,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124466782</v>
+        <v>124466710</v>
       </c>
       <c r="B13" t="n">
-        <v>78810</v>
+        <v>78842</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1845,21 +1836,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1869,10 +1860,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>454914</v>
+        <v>454946</v>
       </c>
       <c r="R13" t="n">
-        <v>6791574</v>
+        <v>6791477</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1931,10 +1922,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124466766</v>
+        <v>124466750</v>
       </c>
       <c r="B14" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1943,38 +1934,47 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>454930</v>
+        <v>454893</v>
       </c>
       <c r="R14" t="n">
-        <v>6791516</v>
+        <v>6791627</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2033,10 +2033,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124466714</v>
+        <v>124466768</v>
       </c>
       <c r="B15" t="n">
-        <v>90977</v>
+        <v>78810</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2045,25 +2045,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2073,10 +2073,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>454969</v>
+        <v>454929</v>
       </c>
       <c r="R15" t="n">
-        <v>6791399</v>
+        <v>6791494</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2135,10 +2135,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124466779</v>
+        <v>124466729</v>
       </c>
       <c r="B16" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2151,21 +2151,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2175,10 +2175,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>454886</v>
+        <v>454901</v>
       </c>
       <c r="R16" t="n">
-        <v>6791653</v>
+        <v>6791638</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2237,10 +2237,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124466769</v>
+        <v>124466711</v>
       </c>
       <c r="B17" t="n">
-        <v>78810</v>
+        <v>78842</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2253,21 +2253,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2277,10 +2277,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>454970</v>
+        <v>454951</v>
       </c>
       <c r="R17" t="n">
-        <v>6791393</v>
+        <v>6791471</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>

--- a/artfynd/A 10282-2024 artfynd.xlsx
+++ b/artfynd/A 10282-2024 artfynd.xlsx
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124466769</v>
+        <v>124466766</v>
       </c>
       <c r="B3" t="n">
         <v>78810</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>454970</v>
+        <v>454930</v>
       </c>
       <c r="R3" t="n">
-        <v>6791393</v>
+        <v>6791516</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,7 +884,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124466766</v>
+        <v>124466782</v>
       </c>
       <c r="B4" t="n">
         <v>78810</v>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>454930</v>
+        <v>454914</v>
       </c>
       <c r="R4" t="n">
-        <v>6791516</v>
+        <v>6791574</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124466782</v>
+        <v>124466762</v>
       </c>
       <c r="B5" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -998,38 +998,47 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>454914</v>
+        <v>454907</v>
       </c>
       <c r="R5" t="n">
-        <v>6791574</v>
+        <v>6791625</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1190,10 +1199,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124466767</v>
+        <v>124466759</v>
       </c>
       <c r="B7" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1202,38 +1211,47 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>454933</v>
+        <v>454956</v>
       </c>
       <c r="R7" t="n">
-        <v>6791499</v>
+        <v>6791469</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1292,10 +1310,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124466759</v>
+        <v>124466768</v>
       </c>
       <c r="B8" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1304,47 +1322,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>454956</v>
+        <v>454929</v>
       </c>
       <c r="R8" t="n">
-        <v>6791469</v>
+        <v>6791494</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1403,10 +1412,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124466714</v>
+        <v>124466767</v>
       </c>
       <c r="B9" t="n">
-        <v>90977</v>
+        <v>78810</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1415,25 +1424,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1443,10 +1452,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>454969</v>
+        <v>454933</v>
       </c>
       <c r="R9" t="n">
-        <v>6791399</v>
+        <v>6791499</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1505,10 +1514,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124466762</v>
+        <v>124466729</v>
       </c>
       <c r="B10" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1517,47 +1526,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>454907</v>
+        <v>454901</v>
       </c>
       <c r="R10" t="n">
-        <v>6791625</v>
+        <v>6791638</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1616,7 +1616,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124466712</v>
+        <v>124466711</v>
       </c>
       <c r="B11" t="n">
         <v>78842</v>
@@ -1656,10 +1656,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>454964</v>
+        <v>454951</v>
       </c>
       <c r="R11" t="n">
-        <v>6791409</v>
+        <v>6791471</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1718,10 +1718,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124466783</v>
+        <v>124466750</v>
       </c>
       <c r="B12" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1730,38 +1730,47 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>454911</v>
+        <v>454893</v>
       </c>
       <c r="R12" t="n">
-        <v>6791571</v>
+        <v>6791627</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1820,10 +1829,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124466710</v>
+        <v>124466714</v>
       </c>
       <c r="B13" t="n">
-        <v>78842</v>
+        <v>90977</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1832,25 +1841,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>185</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1860,10 +1869,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>454946</v>
+        <v>454969</v>
       </c>
       <c r="R13" t="n">
-        <v>6791477</v>
+        <v>6791399</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1922,10 +1931,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124466750</v>
+        <v>124466769</v>
       </c>
       <c r="B14" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1934,47 +1943,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>454893</v>
+        <v>454970</v>
       </c>
       <c r="R14" t="n">
-        <v>6791627</v>
+        <v>6791393</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2033,10 +2033,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124466768</v>
+        <v>124466710</v>
       </c>
       <c r="B15" t="n">
-        <v>78810</v>
+        <v>78842</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2049,21 +2049,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2073,10 +2073,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>454929</v>
+        <v>454946</v>
       </c>
       <c r="R15" t="n">
-        <v>6791494</v>
+        <v>6791477</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2135,10 +2135,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124466729</v>
+        <v>124466712</v>
       </c>
       <c r="B16" t="n">
-        <v>91012</v>
+        <v>78842</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2151,21 +2151,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>185</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2175,10 +2175,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>454901</v>
+        <v>454964</v>
       </c>
       <c r="R16" t="n">
-        <v>6791638</v>
+        <v>6791409</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2237,10 +2237,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124466711</v>
+        <v>124466783</v>
       </c>
       <c r="B17" t="n">
-        <v>78842</v>
+        <v>78810</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2253,21 +2253,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2277,10 +2277,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>454951</v>
+        <v>454911</v>
       </c>
       <c r="R17" t="n">
-        <v>6791471</v>
+        <v>6791571</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>

--- a/artfynd/A 10282-2024 artfynd.xlsx
+++ b/artfynd/A 10282-2024 artfynd.xlsx
@@ -2135,10 +2135,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124466712</v>
+        <v>124466783</v>
       </c>
       <c r="B16" t="n">
-        <v>78842</v>
+        <v>78810</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2151,21 +2151,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2175,10 +2175,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>454964</v>
+        <v>454911</v>
       </c>
       <c r="R16" t="n">
-        <v>6791409</v>
+        <v>6791571</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2237,10 +2237,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124466783</v>
+        <v>124466712</v>
       </c>
       <c r="B17" t="n">
-        <v>78810</v>
+        <v>78842</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2253,21 +2253,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2277,10 +2277,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>454911</v>
+        <v>454964</v>
       </c>
       <c r="R17" t="n">
-        <v>6791571</v>
+        <v>6791409</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>

--- a/artfynd/A 10282-2024 artfynd.xlsx
+++ b/artfynd/A 10282-2024 artfynd.xlsx
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124466766</v>
+        <v>124466767</v>
       </c>
       <c r="B3" t="n">
         <v>78810</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>454930</v>
+        <v>454933</v>
       </c>
       <c r="R3" t="n">
-        <v>6791516</v>
+        <v>6791499</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124466782</v>
+        <v>124466714</v>
       </c>
       <c r="B4" t="n">
-        <v>78810</v>
+        <v>90977</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -896,25 +896,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>454914</v>
+        <v>454969</v>
       </c>
       <c r="R4" t="n">
-        <v>6791574</v>
+        <v>6791399</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124466762</v>
+        <v>124466779</v>
       </c>
       <c r="B5" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -998,47 +998,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>454907</v>
+        <v>454886</v>
       </c>
       <c r="R5" t="n">
-        <v>6791625</v>
+        <v>6791653</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1097,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124466779</v>
+        <v>124466712</v>
       </c>
       <c r="B6" t="n">
-        <v>78810</v>
+        <v>78842</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1113,21 +1104,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1137,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>454886</v>
+        <v>454964</v>
       </c>
       <c r="R6" t="n">
-        <v>6791653</v>
+        <v>6791409</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1199,7 +1190,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124466759</v>
+        <v>124466750</v>
       </c>
       <c r="B7" t="n">
         <v>98101</v>
@@ -1234,7 +1225,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1248,10 +1239,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>454956</v>
+        <v>454893</v>
       </c>
       <c r="R7" t="n">
-        <v>6791469</v>
+        <v>6791627</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1310,10 +1301,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124466768</v>
+        <v>124466711</v>
       </c>
       <c r="B8" t="n">
-        <v>78810</v>
+        <v>78842</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1326,21 +1317,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1350,10 +1341,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>454929</v>
+        <v>454951</v>
       </c>
       <c r="R8" t="n">
-        <v>6791494</v>
+        <v>6791471</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1412,7 +1403,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124466767</v>
+        <v>124466783</v>
       </c>
       <c r="B9" t="n">
         <v>78810</v>
@@ -1452,10 +1443,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>454933</v>
+        <v>454911</v>
       </c>
       <c r="R9" t="n">
-        <v>6791499</v>
+        <v>6791571</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1514,10 +1505,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124466729</v>
+        <v>124466762</v>
       </c>
       <c r="B10" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1526,38 +1517,47 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>454901</v>
+        <v>454907</v>
       </c>
       <c r="R10" t="n">
-        <v>6791638</v>
+        <v>6791625</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1616,10 +1616,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124466711</v>
+        <v>124466759</v>
       </c>
       <c r="B11" t="n">
-        <v>78842</v>
+        <v>98101</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1628,38 +1628,47 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>454951</v>
+        <v>454956</v>
       </c>
       <c r="R11" t="n">
-        <v>6791471</v>
+        <v>6791469</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1718,10 +1727,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124466750</v>
+        <v>124466768</v>
       </c>
       <c r="B12" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1730,47 +1739,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>454893</v>
+        <v>454929</v>
       </c>
       <c r="R12" t="n">
-        <v>6791627</v>
+        <v>6791494</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1829,10 +1829,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124466714</v>
+        <v>124466782</v>
       </c>
       <c r="B13" t="n">
-        <v>90977</v>
+        <v>78810</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1841,25 +1841,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1869,10 +1869,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>454969</v>
+        <v>454914</v>
       </c>
       <c r="R13" t="n">
-        <v>6791399</v>
+        <v>6791574</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1931,7 +1931,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124466769</v>
+        <v>124466766</v>
       </c>
       <c r="B14" t="n">
         <v>78810</v>
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>454970</v>
+        <v>454930</v>
       </c>
       <c r="R14" t="n">
-        <v>6791393</v>
+        <v>6791516</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2135,7 +2135,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124466783</v>
+        <v>124466769</v>
       </c>
       <c r="B16" t="n">
         <v>78810</v>
@@ -2175,10 +2175,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>454911</v>
+        <v>454970</v>
       </c>
       <c r="R16" t="n">
-        <v>6791571</v>
+        <v>6791393</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2237,10 +2237,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124466712</v>
+        <v>124466729</v>
       </c>
       <c r="B17" t="n">
-        <v>78842</v>
+        <v>91012</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2253,21 +2253,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>185</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2277,10 +2277,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>454964</v>
+        <v>454901</v>
       </c>
       <c r="R17" t="n">
-        <v>6791409</v>
+        <v>6791638</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>

--- a/artfynd/A 10282-2024 artfynd.xlsx
+++ b/artfynd/A 10282-2024 artfynd.xlsx
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124466767</v>
+        <v>124466766</v>
       </c>
       <c r="B3" t="n">
         <v>78810</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>454933</v>
+        <v>454930</v>
       </c>
       <c r="R3" t="n">
-        <v>6791499</v>
+        <v>6791516</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124466714</v>
+        <v>124466767</v>
       </c>
       <c r="B4" t="n">
-        <v>90977</v>
+        <v>78810</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -896,25 +896,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>454969</v>
+        <v>454933</v>
       </c>
       <c r="R4" t="n">
-        <v>6791399</v>
+        <v>6791499</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124466779</v>
+        <v>124466750</v>
       </c>
       <c r="B5" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -998,38 +998,47 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>454886</v>
+        <v>454893</v>
       </c>
       <c r="R5" t="n">
-        <v>6791653</v>
+        <v>6791627</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,10 +1097,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124466712</v>
+        <v>124466769</v>
       </c>
       <c r="B6" t="n">
-        <v>78842</v>
+        <v>78810</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1104,21 +1113,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1128,10 +1137,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>454964</v>
+        <v>454970</v>
       </c>
       <c r="R6" t="n">
-        <v>6791409</v>
+        <v>6791393</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1190,10 +1199,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124466750</v>
+        <v>124466768</v>
       </c>
       <c r="B7" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1202,47 +1211,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>454893</v>
+        <v>454929</v>
       </c>
       <c r="R7" t="n">
-        <v>6791627</v>
+        <v>6791494</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1301,7 +1301,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124466711</v>
+        <v>124466712</v>
       </c>
       <c r="B8" t="n">
         <v>78842</v>
@@ -1341,10 +1341,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>454951</v>
+        <v>454964</v>
       </c>
       <c r="R8" t="n">
-        <v>6791471</v>
+        <v>6791409</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1403,7 +1403,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124466783</v>
+        <v>124466779</v>
       </c>
       <c r="B9" t="n">
         <v>78810</v>
@@ -1443,10 +1443,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>454911</v>
+        <v>454886</v>
       </c>
       <c r="R9" t="n">
-        <v>6791571</v>
+        <v>6791653</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1505,10 +1505,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124466762</v>
+        <v>124466710</v>
       </c>
       <c r="B10" t="n">
-        <v>98101</v>
+        <v>78842</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1517,47 +1517,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>454907</v>
+        <v>454946</v>
       </c>
       <c r="R10" t="n">
-        <v>6791625</v>
+        <v>6791477</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1616,10 +1607,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124466759</v>
+        <v>124466783</v>
       </c>
       <c r="B11" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1628,47 +1619,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>454956</v>
+        <v>454911</v>
       </c>
       <c r="R11" t="n">
-        <v>6791469</v>
+        <v>6791571</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1727,10 +1709,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124466768</v>
+        <v>124466729</v>
       </c>
       <c r="B12" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1743,21 +1725,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1767,10 +1749,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>454929</v>
+        <v>454901</v>
       </c>
       <c r="R12" t="n">
-        <v>6791494</v>
+        <v>6791638</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1931,10 +1913,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124466766</v>
+        <v>124466762</v>
       </c>
       <c r="B14" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1943,38 +1925,47 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>454930</v>
+        <v>454907</v>
       </c>
       <c r="R14" t="n">
-        <v>6791516</v>
+        <v>6791625</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2033,10 +2024,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124466710</v>
+        <v>124466714</v>
       </c>
       <c r="B15" t="n">
-        <v>78842</v>
+        <v>90977</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2045,25 +2036,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>185</v>
+        <v>5447</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2073,10 +2064,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>454946</v>
+        <v>454969</v>
       </c>
       <c r="R15" t="n">
-        <v>6791477</v>
+        <v>6791399</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2135,10 +2126,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124466769</v>
+        <v>124466711</v>
       </c>
       <c r="B16" t="n">
-        <v>78810</v>
+        <v>78842</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2151,21 +2142,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2175,10 +2166,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>454970</v>
+        <v>454951</v>
       </c>
       <c r="R16" t="n">
-        <v>6791393</v>
+        <v>6791471</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2237,10 +2228,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124466729</v>
+        <v>124466759</v>
       </c>
       <c r="B17" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2249,38 +2240,47 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>454901</v>
+        <v>454956</v>
       </c>
       <c r="R17" t="n">
-        <v>6791638</v>
+        <v>6791469</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>

--- a/artfynd/A 10282-2024 artfynd.xlsx
+++ b/artfynd/A 10282-2024 artfynd.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124466766</v>
+        <v>124466710</v>
       </c>
       <c r="B3" t="n">
-        <v>78810</v>
+        <v>78842</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>454930</v>
+        <v>454946</v>
       </c>
       <c r="R3" t="n">
-        <v>6791516</v>
+        <v>6791477</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124466767</v>
+        <v>124466712</v>
       </c>
       <c r="B4" t="n">
-        <v>78810</v>
+        <v>78842</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>454933</v>
+        <v>454964</v>
       </c>
       <c r="R4" t="n">
-        <v>6791499</v>
+        <v>6791409</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124466750</v>
+        <v>124466711</v>
       </c>
       <c r="B5" t="n">
-        <v>98101</v>
+        <v>78842</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -998,47 +998,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>454893</v>
+        <v>454951</v>
       </c>
       <c r="R5" t="n">
-        <v>6791627</v>
+        <v>6791471</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1097,7 +1088,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124466769</v>
+        <v>124466783</v>
       </c>
       <c r="B6" t="n">
         <v>78810</v>
@@ -1137,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>454970</v>
+        <v>454911</v>
       </c>
       <c r="R6" t="n">
-        <v>6791393</v>
+        <v>6791571</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1199,7 +1190,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124466768</v>
+        <v>124466779</v>
       </c>
       <c r="B7" t="n">
         <v>78810</v>
@@ -1239,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>454929</v>
+        <v>454886</v>
       </c>
       <c r="R7" t="n">
-        <v>6791494</v>
+        <v>6791653</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1301,10 +1292,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124466712</v>
+        <v>124466766</v>
       </c>
       <c r="B8" t="n">
-        <v>78842</v>
+        <v>78810</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1317,21 +1308,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1341,10 +1332,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>454964</v>
+        <v>454930</v>
       </c>
       <c r="R8" t="n">
-        <v>6791409</v>
+        <v>6791516</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1403,10 +1394,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124466779</v>
+        <v>124466729</v>
       </c>
       <c r="B9" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1419,21 +1410,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1443,10 +1434,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>454886</v>
+        <v>454901</v>
       </c>
       <c r="R9" t="n">
-        <v>6791653</v>
+        <v>6791638</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1505,10 +1496,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124466710</v>
+        <v>124466782</v>
       </c>
       <c r="B10" t="n">
-        <v>78842</v>
+        <v>78810</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1521,21 +1512,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1545,10 +1536,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>454946</v>
+        <v>454914</v>
       </c>
       <c r="R10" t="n">
-        <v>6791477</v>
+        <v>6791574</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1607,10 +1598,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124466783</v>
+        <v>124466759</v>
       </c>
       <c r="B11" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1619,38 +1610,47 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>454911</v>
+        <v>454956</v>
       </c>
       <c r="R11" t="n">
-        <v>6791571</v>
+        <v>6791469</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1709,10 +1709,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124466729</v>
+        <v>124466750</v>
       </c>
       <c r="B12" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1721,38 +1721,47 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>454901</v>
+        <v>454893</v>
       </c>
       <c r="R12" t="n">
-        <v>6791638</v>
+        <v>6791627</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1811,7 +1820,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124466782</v>
+        <v>124466769</v>
       </c>
       <c r="B13" t="n">
         <v>78810</v>
@@ -1851,10 +1860,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>454914</v>
+        <v>454970</v>
       </c>
       <c r="R13" t="n">
-        <v>6791574</v>
+        <v>6791393</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1913,10 +1922,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124466762</v>
+        <v>124466714</v>
       </c>
       <c r="B14" t="n">
-        <v>98101</v>
+        <v>90977</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1925,47 +1934,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>454907</v>
+        <v>454969</v>
       </c>
       <c r="R14" t="n">
-        <v>6791625</v>
+        <v>6791399</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2024,10 +2024,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124466714</v>
+        <v>124466768</v>
       </c>
       <c r="B15" t="n">
-        <v>90977</v>
+        <v>78810</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2036,25 +2036,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2064,10 +2064,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>454969</v>
+        <v>454929</v>
       </c>
       <c r="R15" t="n">
-        <v>6791399</v>
+        <v>6791494</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2126,10 +2126,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124466711</v>
+        <v>124466767</v>
       </c>
       <c r="B16" t="n">
-        <v>78842</v>
+        <v>78810</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2142,21 +2142,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2166,10 +2166,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>454951</v>
+        <v>454933</v>
       </c>
       <c r="R16" t="n">
-        <v>6791471</v>
+        <v>6791499</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2228,7 +2228,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124466759</v>
+        <v>124466762</v>
       </c>
       <c r="B17" t="n">
         <v>98101</v>
@@ -2277,10 +2277,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>454956</v>
+        <v>454907</v>
       </c>
       <c r="R17" t="n">
-        <v>6791469</v>
+        <v>6791625</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>

--- a/artfynd/A 10282-2024 artfynd.xlsx
+++ b/artfynd/A 10282-2024 artfynd.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124466710</v>
+        <v>124466782</v>
       </c>
       <c r="B3" t="n">
-        <v>78842</v>
+        <v>78810</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>454946</v>
+        <v>454914</v>
       </c>
       <c r="R3" t="n">
-        <v>6791477</v>
+        <v>6791574</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124466712</v>
+        <v>124466759</v>
       </c>
       <c r="B4" t="n">
-        <v>78842</v>
+        <v>98101</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -896,38 +896,47 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>454964</v>
+        <v>454956</v>
       </c>
       <c r="R4" t="n">
-        <v>6791409</v>
+        <v>6791469</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,10 +995,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124466711</v>
+        <v>124466779</v>
       </c>
       <c r="B5" t="n">
-        <v>78842</v>
+        <v>78810</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,21 +1011,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1035,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>454951</v>
+        <v>454886</v>
       </c>
       <c r="R5" t="n">
-        <v>6791471</v>
+        <v>6791653</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,10 +1097,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124466783</v>
+        <v>124466762</v>
       </c>
       <c r="B6" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1100,38 +1109,47 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>454911</v>
+        <v>454907</v>
       </c>
       <c r="R6" t="n">
-        <v>6791571</v>
+        <v>6791625</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1190,7 +1208,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124466779</v>
+        <v>124466768</v>
       </c>
       <c r="B7" t="n">
         <v>78810</v>
@@ -1230,10 +1248,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>454886</v>
+        <v>454929</v>
       </c>
       <c r="R7" t="n">
-        <v>6791653</v>
+        <v>6791494</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1292,10 +1310,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124466766</v>
+        <v>124466711</v>
       </c>
       <c r="B8" t="n">
-        <v>78810</v>
+        <v>78842</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1308,21 +1326,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1332,10 +1350,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>454930</v>
+        <v>454951</v>
       </c>
       <c r="R8" t="n">
-        <v>6791516</v>
+        <v>6791471</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1394,10 +1412,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124466729</v>
+        <v>124466712</v>
       </c>
       <c r="B9" t="n">
-        <v>91012</v>
+        <v>78842</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1410,21 +1428,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>185</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1434,10 +1452,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>454901</v>
+        <v>454964</v>
       </c>
       <c r="R9" t="n">
-        <v>6791638</v>
+        <v>6791409</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1496,7 +1514,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124466782</v>
+        <v>124466783</v>
       </c>
       <c r="B10" t="n">
         <v>78810</v>
@@ -1536,10 +1554,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>454914</v>
+        <v>454911</v>
       </c>
       <c r="R10" t="n">
-        <v>6791574</v>
+        <v>6791571</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1598,10 +1616,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124466759</v>
+        <v>124466767</v>
       </c>
       <c r="B11" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1610,47 +1628,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>454956</v>
+        <v>454933</v>
       </c>
       <c r="R11" t="n">
-        <v>6791469</v>
+        <v>6791499</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1709,10 +1718,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124466750</v>
+        <v>124466766</v>
       </c>
       <c r="B12" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1721,47 +1730,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>454893</v>
+        <v>454930</v>
       </c>
       <c r="R12" t="n">
-        <v>6791627</v>
+        <v>6791516</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2024,10 +2024,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124466768</v>
+        <v>124466750</v>
       </c>
       <c r="B15" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2036,38 +2036,47 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>454929</v>
+        <v>454893</v>
       </c>
       <c r="R15" t="n">
-        <v>6791494</v>
+        <v>6791627</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2126,10 +2135,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124466767</v>
+        <v>124466729</v>
       </c>
       <c r="B16" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2142,21 +2151,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2166,10 +2175,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>454933</v>
+        <v>454901</v>
       </c>
       <c r="R16" t="n">
-        <v>6791499</v>
+        <v>6791638</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2228,10 +2237,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124466762</v>
+        <v>124466710</v>
       </c>
       <c r="B17" t="n">
-        <v>98101</v>
+        <v>78842</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2240,47 +2249,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>454907</v>
+        <v>454946</v>
       </c>
       <c r="R17" t="n">
-        <v>6791625</v>
+        <v>6791477</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>

--- a/artfynd/A 10282-2024 artfynd.xlsx
+++ b/artfynd/A 10282-2024 artfynd.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124466782</v>
+        <v>124466729</v>
       </c>
       <c r="B3" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>454914</v>
+        <v>454901</v>
       </c>
       <c r="R3" t="n">
-        <v>6791574</v>
+        <v>6791638</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124466759</v>
+        <v>124466779</v>
       </c>
       <c r="B4" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -896,47 +896,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>454956</v>
+        <v>454886</v>
       </c>
       <c r="R4" t="n">
-        <v>6791469</v>
+        <v>6791653</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -995,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124466779</v>
+        <v>124466712</v>
       </c>
       <c r="B5" t="n">
-        <v>78810</v>
+        <v>78842</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1011,21 +1002,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1035,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>454886</v>
+        <v>454964</v>
       </c>
       <c r="R5" t="n">
-        <v>6791653</v>
+        <v>6791409</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1097,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124466762</v>
+        <v>124466767</v>
       </c>
       <c r="B6" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1109,47 +1100,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>454907</v>
+        <v>454933</v>
       </c>
       <c r="R6" t="n">
-        <v>6791625</v>
+        <v>6791499</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1208,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124466768</v>
+        <v>124466710</v>
       </c>
       <c r="B7" t="n">
-        <v>78810</v>
+        <v>78842</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1224,21 +1206,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1248,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>454929</v>
+        <v>454946</v>
       </c>
       <c r="R7" t="n">
-        <v>6791494</v>
+        <v>6791477</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1310,10 +1292,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124466711</v>
+        <v>124466750</v>
       </c>
       <c r="B8" t="n">
-        <v>78842</v>
+        <v>98101</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1322,38 +1304,47 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>454951</v>
+        <v>454893</v>
       </c>
       <c r="R8" t="n">
-        <v>6791471</v>
+        <v>6791627</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1412,10 +1403,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124466712</v>
+        <v>124466762</v>
       </c>
       <c r="B9" t="n">
-        <v>78842</v>
+        <v>98101</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1424,38 +1415,47 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>454964</v>
+        <v>454907</v>
       </c>
       <c r="R9" t="n">
-        <v>6791409</v>
+        <v>6791625</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1514,7 +1514,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124466783</v>
+        <v>124466782</v>
       </c>
       <c r="B10" t="n">
         <v>78810</v>
@@ -1554,10 +1554,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>454911</v>
+        <v>454914</v>
       </c>
       <c r="R10" t="n">
-        <v>6791571</v>
+        <v>6791574</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1616,10 +1616,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124466767</v>
+        <v>124466759</v>
       </c>
       <c r="B11" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1628,38 +1628,47 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>454933</v>
+        <v>454956</v>
       </c>
       <c r="R11" t="n">
-        <v>6791499</v>
+        <v>6791469</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1718,7 +1727,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124466766</v>
+        <v>124466769</v>
       </c>
       <c r="B12" t="n">
         <v>78810</v>
@@ -1758,10 +1767,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>454930</v>
+        <v>454970</v>
       </c>
       <c r="R12" t="n">
-        <v>6791516</v>
+        <v>6791393</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1820,7 +1829,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124466769</v>
+        <v>124466766</v>
       </c>
       <c r="B13" t="n">
         <v>78810</v>
@@ -1860,10 +1869,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>454970</v>
+        <v>454930</v>
       </c>
       <c r="R13" t="n">
-        <v>6791393</v>
+        <v>6791516</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1922,10 +1931,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124466714</v>
+        <v>124466768</v>
       </c>
       <c r="B14" t="n">
-        <v>90977</v>
+        <v>78810</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1934,25 +1943,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1962,10 +1971,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>454969</v>
+        <v>454929</v>
       </c>
       <c r="R14" t="n">
-        <v>6791399</v>
+        <v>6791494</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2024,10 +2033,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124466750</v>
+        <v>124466714</v>
       </c>
       <c r="B15" t="n">
-        <v>98101</v>
+        <v>90977</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2036,47 +2045,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>454893</v>
+        <v>454969</v>
       </c>
       <c r="R15" t="n">
-        <v>6791627</v>
+        <v>6791399</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2135,10 +2135,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124466729</v>
+        <v>124466711</v>
       </c>
       <c r="B16" t="n">
-        <v>91012</v>
+        <v>78842</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2151,21 +2151,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>185</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2175,10 +2175,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>454901</v>
+        <v>454951</v>
       </c>
       <c r="R16" t="n">
-        <v>6791638</v>
+        <v>6791471</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2237,10 +2237,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124466710</v>
+        <v>124466783</v>
       </c>
       <c r="B17" t="n">
-        <v>78842</v>
+        <v>78810</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2253,21 +2253,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2277,10 +2277,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>454946</v>
+        <v>454911</v>
       </c>
       <c r="R17" t="n">
-        <v>6791477</v>
+        <v>6791571</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>

--- a/artfynd/A 10282-2024 artfynd.xlsx
+++ b/artfynd/A 10282-2024 artfynd.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124466729</v>
+        <v>124466711</v>
       </c>
       <c r="B3" t="n">
-        <v>91012</v>
+        <v>78842</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>185</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>454901</v>
+        <v>454951</v>
       </c>
       <c r="R3" t="n">
-        <v>6791638</v>
+        <v>6791471</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124466779</v>
+        <v>124466714</v>
       </c>
       <c r="B4" t="n">
-        <v>78810</v>
+        <v>90977</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -896,25 +896,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>454886</v>
+        <v>454969</v>
       </c>
       <c r="R4" t="n">
-        <v>6791653</v>
+        <v>6791399</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124466712</v>
+        <v>124466779</v>
       </c>
       <c r="B5" t="n">
-        <v>78842</v>
+        <v>78810</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,21 +1002,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>454964</v>
+        <v>454886</v>
       </c>
       <c r="R5" t="n">
-        <v>6791409</v>
+        <v>6791653</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,7 +1088,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124466767</v>
+        <v>124466766</v>
       </c>
       <c r="B6" t="n">
         <v>78810</v>
@@ -1128,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>454933</v>
+        <v>454930</v>
       </c>
       <c r="R6" t="n">
-        <v>6791499</v>
+        <v>6791516</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1190,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124466710</v>
+        <v>124466783</v>
       </c>
       <c r="B7" t="n">
-        <v>78842</v>
+        <v>78810</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1206,21 +1206,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1230,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>454946</v>
+        <v>454911</v>
       </c>
       <c r="R7" t="n">
-        <v>6791477</v>
+        <v>6791571</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1292,10 +1292,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124466750</v>
+        <v>124466729</v>
       </c>
       <c r="B8" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1304,47 +1304,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>454893</v>
+        <v>454901</v>
       </c>
       <c r="R8" t="n">
-        <v>6791627</v>
+        <v>6791638</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1403,7 +1394,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124466762</v>
+        <v>124466750</v>
       </c>
       <c r="B9" t="n">
         <v>98101</v>
@@ -1438,7 +1429,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1452,10 +1443,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>454907</v>
+        <v>454893</v>
       </c>
       <c r="R9" t="n">
-        <v>6791625</v>
+        <v>6791627</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1514,7 +1505,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124466782</v>
+        <v>124466767</v>
       </c>
       <c r="B10" t="n">
         <v>78810</v>
@@ -1554,10 +1545,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>454914</v>
+        <v>454933</v>
       </c>
       <c r="R10" t="n">
-        <v>6791574</v>
+        <v>6791499</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1616,10 +1607,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124466759</v>
+        <v>124466712</v>
       </c>
       <c r="B11" t="n">
-        <v>98101</v>
+        <v>78842</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1628,47 +1619,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>454956</v>
+        <v>454964</v>
       </c>
       <c r="R11" t="n">
-        <v>6791469</v>
+        <v>6791409</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1727,10 +1709,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124466769</v>
+        <v>124466710</v>
       </c>
       <c r="B12" t="n">
-        <v>78810</v>
+        <v>78842</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1743,21 +1725,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1767,10 +1749,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>454970</v>
+        <v>454946</v>
       </c>
       <c r="R12" t="n">
-        <v>6791393</v>
+        <v>6791477</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1829,10 +1811,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124466766</v>
+        <v>124466759</v>
       </c>
       <c r="B13" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1841,38 +1823,47 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>454930</v>
+        <v>454956</v>
       </c>
       <c r="R13" t="n">
-        <v>6791516</v>
+        <v>6791469</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1931,10 +1922,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124466768</v>
+        <v>124466762</v>
       </c>
       <c r="B14" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1943,38 +1934,47 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>454929</v>
+        <v>454907</v>
       </c>
       <c r="R14" t="n">
-        <v>6791494</v>
+        <v>6791625</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2033,10 +2033,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124466714</v>
+        <v>124466768</v>
       </c>
       <c r="B15" t="n">
-        <v>90977</v>
+        <v>78810</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2045,25 +2045,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2073,10 +2073,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>454969</v>
+        <v>454929</v>
       </c>
       <c r="R15" t="n">
-        <v>6791399</v>
+        <v>6791494</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2135,10 +2135,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124466711</v>
+        <v>124466769</v>
       </c>
       <c r="B16" t="n">
-        <v>78842</v>
+        <v>78810</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2151,21 +2151,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2175,10 +2175,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>454951</v>
+        <v>454970</v>
       </c>
       <c r="R16" t="n">
-        <v>6791471</v>
+        <v>6791393</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2237,7 +2237,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124466783</v>
+        <v>124466782</v>
       </c>
       <c r="B17" t="n">
         <v>78810</v>
@@ -2277,10 +2277,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>454911</v>
+        <v>454914</v>
       </c>
       <c r="R17" t="n">
-        <v>6791571</v>
+        <v>6791574</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>

--- a/artfynd/A 10282-2024 artfynd.xlsx
+++ b/artfynd/A 10282-2024 artfynd.xlsx
@@ -1922,10 +1922,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124466762</v>
+        <v>124466768</v>
       </c>
       <c r="B14" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1934,47 +1934,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>454907</v>
+        <v>454929</v>
       </c>
       <c r="R14" t="n">
-        <v>6791625</v>
+        <v>6791494</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2033,10 +2024,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124466768</v>
+        <v>124466762</v>
       </c>
       <c r="B15" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2045,38 +2036,47 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>454929</v>
+        <v>454907</v>
       </c>
       <c r="R15" t="n">
-        <v>6791494</v>
+        <v>6791625</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>

--- a/artfynd/A 10282-2024 artfynd.xlsx
+++ b/artfynd/A 10282-2024 artfynd.xlsx
@@ -1505,10 +1505,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124466767</v>
+        <v>124466712</v>
       </c>
       <c r="B10" t="n">
-        <v>78810</v>
+        <v>78842</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1521,21 +1521,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1545,10 +1545,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>454933</v>
+        <v>454964</v>
       </c>
       <c r="R10" t="n">
-        <v>6791499</v>
+        <v>6791409</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1607,7 +1607,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124466712</v>
+        <v>124466710</v>
       </c>
       <c r="B11" t="n">
         <v>78842</v>
@@ -1647,10 +1647,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>454964</v>
+        <v>454946</v>
       </c>
       <c r="R11" t="n">
-        <v>6791409</v>
+        <v>6791477</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1709,10 +1709,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124466710</v>
+        <v>124466767</v>
       </c>
       <c r="B12" t="n">
-        <v>78842</v>
+        <v>78810</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1725,21 +1725,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>454946</v>
+        <v>454933</v>
       </c>
       <c r="R12" t="n">
-        <v>6791477</v>
+        <v>6791499</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 10282-2024 artfynd.xlsx
+++ b/artfynd/A 10282-2024 artfynd.xlsx
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124466711</v>
+        <v>124466710</v>
       </c>
       <c r="B3" t="n">
         <v>78842</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>454951</v>
+        <v>454946</v>
       </c>
       <c r="R3" t="n">
-        <v>6791471</v>
+        <v>6791477</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124466714</v>
+        <v>124466769</v>
       </c>
       <c r="B4" t="n">
-        <v>90977</v>
+        <v>78810</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -896,25 +896,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>454969</v>
+        <v>454970</v>
       </c>
       <c r="R4" t="n">
-        <v>6791399</v>
+        <v>6791393</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124466779</v>
+        <v>124466750</v>
       </c>
       <c r="B5" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -998,38 +998,47 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>454886</v>
+        <v>454893</v>
       </c>
       <c r="R5" t="n">
-        <v>6791653</v>
+        <v>6791627</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1190,10 +1199,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124466783</v>
+        <v>124466714</v>
       </c>
       <c r="B7" t="n">
-        <v>78810</v>
+        <v>90977</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1202,25 +1211,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1230,10 +1239,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>454911</v>
+        <v>454969</v>
       </c>
       <c r="R7" t="n">
-        <v>6791571</v>
+        <v>6791399</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1292,10 +1301,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124466729</v>
+        <v>124466779</v>
       </c>
       <c r="B8" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1308,21 +1317,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1332,10 +1341,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>454901</v>
+        <v>454886</v>
       </c>
       <c r="R8" t="n">
-        <v>6791638</v>
+        <v>6791653</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1394,10 +1403,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124466750</v>
+        <v>124466729</v>
       </c>
       <c r="B9" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1406,47 +1415,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>454893</v>
+        <v>454901</v>
       </c>
       <c r="R9" t="n">
-        <v>6791627</v>
+        <v>6791638</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1505,10 +1505,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124466712</v>
+        <v>124466759</v>
       </c>
       <c r="B10" t="n">
-        <v>78842</v>
+        <v>98101</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1517,38 +1517,47 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>454964</v>
+        <v>454956</v>
       </c>
       <c r="R10" t="n">
-        <v>6791409</v>
+        <v>6791469</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1607,10 +1616,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124466710</v>
+        <v>124466767</v>
       </c>
       <c r="B11" t="n">
-        <v>78842</v>
+        <v>78810</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1623,21 +1632,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1647,10 +1656,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>454946</v>
+        <v>454933</v>
       </c>
       <c r="R11" t="n">
-        <v>6791477</v>
+        <v>6791499</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1709,7 +1718,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124466767</v>
+        <v>124466783</v>
       </c>
       <c r="B12" t="n">
         <v>78810</v>
@@ -1749,10 +1758,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>454933</v>
+        <v>454911</v>
       </c>
       <c r="R12" t="n">
-        <v>6791499</v>
+        <v>6791571</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1811,7 +1820,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124466759</v>
+        <v>124466762</v>
       </c>
       <c r="B13" t="n">
         <v>98101</v>
@@ -1860,10 +1869,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>454956</v>
+        <v>454907</v>
       </c>
       <c r="R13" t="n">
-        <v>6791469</v>
+        <v>6791625</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1922,7 +1931,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124466768</v>
+        <v>124466782</v>
       </c>
       <c r="B14" t="n">
         <v>78810</v>
@@ -1962,10 +1971,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>454929</v>
+        <v>454914</v>
       </c>
       <c r="R14" t="n">
-        <v>6791494</v>
+        <v>6791574</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2024,10 +2033,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124466762</v>
+        <v>124466712</v>
       </c>
       <c r="B15" t="n">
-        <v>98101</v>
+        <v>78842</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2036,47 +2045,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>454907</v>
+        <v>454964</v>
       </c>
       <c r="R15" t="n">
-        <v>6791625</v>
+        <v>6791409</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2135,10 +2135,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124466769</v>
+        <v>124466711</v>
       </c>
       <c r="B16" t="n">
-        <v>78810</v>
+        <v>78842</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2151,21 +2151,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2175,10 +2175,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>454970</v>
+        <v>454951</v>
       </c>
       <c r="R16" t="n">
-        <v>6791393</v>
+        <v>6791471</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2237,7 +2237,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124466782</v>
+        <v>124466768</v>
       </c>
       <c r="B17" t="n">
         <v>78810</v>
@@ -2277,10 +2277,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>454914</v>
+        <v>454929</v>
       </c>
       <c r="R17" t="n">
-        <v>6791574</v>
+        <v>6791494</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>

--- a/artfynd/A 10282-2024 artfynd.xlsx
+++ b/artfynd/A 10282-2024 artfynd.xlsx
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124466710</v>
+        <v>124466711</v>
       </c>
       <c r="B3" t="n">
         <v>78842</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>454946</v>
+        <v>454951</v>
       </c>
       <c r="R3" t="n">
-        <v>6791477</v>
+        <v>6791471</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,7 +884,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124466769</v>
+        <v>124466768</v>
       </c>
       <c r="B4" t="n">
         <v>78810</v>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>454970</v>
+        <v>454929</v>
       </c>
       <c r="R4" t="n">
-        <v>6791393</v>
+        <v>6791494</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,7 +986,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124466750</v>
+        <v>124466762</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1021,7 +1021,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1035,10 +1035,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>454893</v>
+        <v>454907</v>
       </c>
       <c r="R5" t="n">
-        <v>6791627</v>
+        <v>6791625</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1097,7 +1097,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124466766</v>
+        <v>124466779</v>
       </c>
       <c r="B6" t="n">
         <v>78810</v>
@@ -1137,10 +1137,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>454930</v>
+        <v>454886</v>
       </c>
       <c r="R6" t="n">
-        <v>6791516</v>
+        <v>6791653</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1199,10 +1199,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124466714</v>
+        <v>124466710</v>
       </c>
       <c r="B7" t="n">
-        <v>90977</v>
+        <v>78842</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1211,25 +1211,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>185</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1239,10 +1239,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>454969</v>
+        <v>454946</v>
       </c>
       <c r="R7" t="n">
-        <v>6791399</v>
+        <v>6791477</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1301,10 +1301,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124466779</v>
+        <v>124466729</v>
       </c>
       <c r="B8" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1317,21 +1317,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1341,10 +1341,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>454886</v>
+        <v>454901</v>
       </c>
       <c r="R8" t="n">
-        <v>6791653</v>
+        <v>6791638</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1403,10 +1403,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124466729</v>
+        <v>124466767</v>
       </c>
       <c r="B9" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1419,21 +1419,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1443,10 +1443,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>454901</v>
+        <v>454933</v>
       </c>
       <c r="R9" t="n">
-        <v>6791638</v>
+        <v>6791499</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1505,10 +1505,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124466759</v>
+        <v>124466769</v>
       </c>
       <c r="B10" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1517,47 +1517,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>454956</v>
+        <v>454970</v>
       </c>
       <c r="R10" t="n">
-        <v>6791469</v>
+        <v>6791393</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1616,7 +1607,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124466767</v>
+        <v>124466766</v>
       </c>
       <c r="B11" t="n">
         <v>78810</v>
@@ -1656,10 +1647,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>454933</v>
+        <v>454930</v>
       </c>
       <c r="R11" t="n">
-        <v>6791499</v>
+        <v>6791516</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1718,10 +1709,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124466783</v>
+        <v>124466759</v>
       </c>
       <c r="B12" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1730,38 +1721,47 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>454911</v>
+        <v>454956</v>
       </c>
       <c r="R12" t="n">
-        <v>6791571</v>
+        <v>6791469</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1820,10 +1820,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124466762</v>
+        <v>124466783</v>
       </c>
       <c r="B13" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1832,47 +1832,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>454907</v>
+        <v>454911</v>
       </c>
       <c r="R13" t="n">
-        <v>6791625</v>
+        <v>6791571</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1931,10 +1922,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124466782</v>
+        <v>124466750</v>
       </c>
       <c r="B14" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1943,38 +1934,47 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>454914</v>
+        <v>454893</v>
       </c>
       <c r="R14" t="n">
-        <v>6791574</v>
+        <v>6791627</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2135,10 +2135,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124466711</v>
+        <v>124466714</v>
       </c>
       <c r="B16" t="n">
-        <v>78842</v>
+        <v>90977</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2147,25 +2147,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>185</v>
+        <v>5447</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2175,10 +2175,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>454951</v>
+        <v>454969</v>
       </c>
       <c r="R16" t="n">
-        <v>6791471</v>
+        <v>6791399</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2237,7 +2237,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124466768</v>
+        <v>124466782</v>
       </c>
       <c r="B17" t="n">
         <v>78810</v>
@@ -2277,10 +2277,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>454929</v>
+        <v>454914</v>
       </c>
       <c r="R17" t="n">
-        <v>6791494</v>
+        <v>6791574</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>

--- a/artfynd/A 10282-2024 artfynd.xlsx
+++ b/artfynd/A 10282-2024 artfynd.xlsx
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124466711</v>
+        <v>124466712</v>
       </c>
       <c r="B3" t="n">
         <v>78842</v>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>454951</v>
+        <v>454964</v>
       </c>
       <c r="R3" t="n">
-        <v>6791471</v>
+        <v>6791409</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124466768</v>
+        <v>124466714</v>
       </c>
       <c r="B4" t="n">
-        <v>78810</v>
+        <v>90977</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -896,25 +896,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>454929</v>
+        <v>454969</v>
       </c>
       <c r="R4" t="n">
-        <v>6791494</v>
+        <v>6791399</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124466762</v>
+        <v>124466767</v>
       </c>
       <c r="B5" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -998,47 +998,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>454907</v>
+        <v>454933</v>
       </c>
       <c r="R5" t="n">
-        <v>6791625</v>
+        <v>6791499</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1097,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124466779</v>
+        <v>124466729</v>
       </c>
       <c r="B6" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1113,21 +1104,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1137,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>454886</v>
+        <v>454901</v>
       </c>
       <c r="R6" t="n">
-        <v>6791653</v>
+        <v>6791638</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1199,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124466710</v>
+        <v>124466766</v>
       </c>
       <c r="B7" t="n">
-        <v>78842</v>
+        <v>78810</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1215,21 +1206,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1239,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>454946</v>
+        <v>454930</v>
       </c>
       <c r="R7" t="n">
-        <v>6791477</v>
+        <v>6791516</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1301,10 +1292,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124466729</v>
+        <v>124466710</v>
       </c>
       <c r="B8" t="n">
-        <v>91012</v>
+        <v>78842</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1317,21 +1308,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>185</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1341,10 +1332,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>454901</v>
+        <v>454946</v>
       </c>
       <c r="R8" t="n">
-        <v>6791638</v>
+        <v>6791477</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1403,10 +1394,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124466767</v>
+        <v>124466711</v>
       </c>
       <c r="B9" t="n">
-        <v>78810</v>
+        <v>78842</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1419,21 +1410,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1443,10 +1434,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>454933</v>
+        <v>454951</v>
       </c>
       <c r="R9" t="n">
-        <v>6791499</v>
+        <v>6791471</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1505,7 +1496,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124466769</v>
+        <v>124466768</v>
       </c>
       <c r="B10" t="n">
         <v>78810</v>
@@ -1545,10 +1536,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>454970</v>
+        <v>454929</v>
       </c>
       <c r="R10" t="n">
-        <v>6791393</v>
+        <v>6791494</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1607,10 +1598,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124466766</v>
+        <v>124466759</v>
       </c>
       <c r="B11" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1619,38 +1610,47 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>454930</v>
+        <v>454956</v>
       </c>
       <c r="R11" t="n">
-        <v>6791516</v>
+        <v>6791469</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1709,10 +1709,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124466759</v>
+        <v>124466779</v>
       </c>
       <c r="B12" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1721,47 +1721,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>454956</v>
+        <v>454886</v>
       </c>
       <c r="R12" t="n">
-        <v>6791469</v>
+        <v>6791653</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1820,7 +1811,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124466783</v>
+        <v>124466782</v>
       </c>
       <c r="B13" t="n">
         <v>78810</v>
@@ -1860,10 +1851,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>454911</v>
+        <v>454914</v>
       </c>
       <c r="R13" t="n">
-        <v>6791571</v>
+        <v>6791574</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1922,7 +1913,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124466750</v>
+        <v>124466762</v>
       </c>
       <c r="B14" t="n">
         <v>98101</v>
@@ -1957,7 +1948,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1971,10 +1962,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>454893</v>
+        <v>454907</v>
       </c>
       <c r="R14" t="n">
-        <v>6791627</v>
+        <v>6791625</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2033,10 +2024,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124466712</v>
+        <v>124466750</v>
       </c>
       <c r="B15" t="n">
-        <v>78842</v>
+        <v>98101</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2045,38 +2036,47 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>454964</v>
+        <v>454893</v>
       </c>
       <c r="R15" t="n">
-        <v>6791409</v>
+        <v>6791627</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2135,10 +2135,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124466714</v>
+        <v>124466769</v>
       </c>
       <c r="B16" t="n">
-        <v>90977</v>
+        <v>78810</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2147,25 +2147,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2175,10 +2175,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>454969</v>
+        <v>454970</v>
       </c>
       <c r="R16" t="n">
-        <v>6791399</v>
+        <v>6791393</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2237,7 +2237,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124466782</v>
+        <v>124466783</v>
       </c>
       <c r="B17" t="n">
         <v>78810</v>
@@ -2277,10 +2277,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>454914</v>
+        <v>454911</v>
       </c>
       <c r="R17" t="n">
-        <v>6791574</v>
+        <v>6791571</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>

--- a/artfynd/A 10282-2024 artfynd.xlsx
+++ b/artfynd/A 10282-2024 artfynd.xlsx
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124466712</v>
+        <v>124466769</v>
       </c>
       <c r="B3" t="n">
-        <v>78842</v>
+        <v>78810</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>454964</v>
+        <v>454970</v>
       </c>
       <c r="R3" t="n">
-        <v>6791409</v>
+        <v>6791393</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124466714</v>
+        <v>124466750</v>
       </c>
       <c r="B4" t="n">
-        <v>90977</v>
+        <v>98101</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -896,38 +896,47 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>454969</v>
+        <v>454893</v>
       </c>
       <c r="R4" t="n">
-        <v>6791399</v>
+        <v>6791627</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,10 +995,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124466767</v>
+        <v>124466711</v>
       </c>
       <c r="B5" t="n">
-        <v>78810</v>
+        <v>78842</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,21 +1011,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1035,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>454933</v>
+        <v>454951</v>
       </c>
       <c r="R5" t="n">
-        <v>6791499</v>
+        <v>6791471</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,10 +1097,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124466729</v>
+        <v>124466766</v>
       </c>
       <c r="B6" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1104,21 +1113,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1128,10 +1137,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>454901</v>
+        <v>454930</v>
       </c>
       <c r="R6" t="n">
-        <v>6791638</v>
+        <v>6791516</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1190,7 +1199,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124466766</v>
+        <v>124466768</v>
       </c>
       <c r="B7" t="n">
         <v>78810</v>
@@ -1230,10 +1239,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>454930</v>
+        <v>454929</v>
       </c>
       <c r="R7" t="n">
-        <v>6791516</v>
+        <v>6791494</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1292,10 +1301,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124466710</v>
+        <v>124466782</v>
       </c>
       <c r="B8" t="n">
-        <v>78842</v>
+        <v>78810</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1308,21 +1317,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1332,10 +1341,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>454946</v>
+        <v>454914</v>
       </c>
       <c r="R8" t="n">
-        <v>6791477</v>
+        <v>6791574</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1394,7 +1403,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124466711</v>
+        <v>124466712</v>
       </c>
       <c r="B9" t="n">
         <v>78842</v>
@@ -1434,10 +1443,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>454951</v>
+        <v>454964</v>
       </c>
       <c r="R9" t="n">
-        <v>6791471</v>
+        <v>6791409</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1496,10 +1505,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124466768</v>
+        <v>124466759</v>
       </c>
       <c r="B10" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1508,38 +1517,47 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>454929</v>
+        <v>454956</v>
       </c>
       <c r="R10" t="n">
-        <v>6791494</v>
+        <v>6791469</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1598,10 +1616,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124466759</v>
+        <v>124466714</v>
       </c>
       <c r="B11" t="n">
-        <v>98101</v>
+        <v>90977</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1610,47 +1628,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>454956</v>
+        <v>454969</v>
       </c>
       <c r="R11" t="n">
-        <v>6791469</v>
+        <v>6791399</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1709,10 +1718,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124466779</v>
+        <v>124466729</v>
       </c>
       <c r="B12" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1725,21 +1734,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1749,10 +1758,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>454886</v>
+        <v>454901</v>
       </c>
       <c r="R12" t="n">
-        <v>6791653</v>
+        <v>6791638</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1811,10 +1820,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124466782</v>
+        <v>124466710</v>
       </c>
       <c r="B13" t="n">
-        <v>78810</v>
+        <v>78842</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1827,21 +1836,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1851,10 +1860,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>454914</v>
+        <v>454946</v>
       </c>
       <c r="R13" t="n">
-        <v>6791574</v>
+        <v>6791477</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1913,10 +1922,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124466762</v>
+        <v>124466783</v>
       </c>
       <c r="B14" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1925,47 +1934,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>454907</v>
+        <v>454911</v>
       </c>
       <c r="R14" t="n">
-        <v>6791625</v>
+        <v>6791571</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2024,10 +2024,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124466750</v>
+        <v>124466767</v>
       </c>
       <c r="B15" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2036,47 +2036,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>454893</v>
+        <v>454933</v>
       </c>
       <c r="R15" t="n">
-        <v>6791627</v>
+        <v>6791499</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2135,7 +2126,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124466769</v>
+        <v>124466779</v>
       </c>
       <c r="B16" t="n">
         <v>78810</v>
@@ -2175,10 +2166,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>454970</v>
+        <v>454886</v>
       </c>
       <c r="R16" t="n">
-        <v>6791393</v>
+        <v>6791653</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2237,10 +2228,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124466783</v>
+        <v>124466762</v>
       </c>
       <c r="B17" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2249,38 +2240,47 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>454911</v>
+        <v>454907</v>
       </c>
       <c r="R17" t="n">
-        <v>6791571</v>
+        <v>6791625</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>

--- a/artfynd/A 10282-2024 artfynd.xlsx
+++ b/artfynd/A 10282-2024 artfynd.xlsx
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124466750</v>
+        <v>124466711</v>
       </c>
       <c r="B4" t="n">
-        <v>98101</v>
+        <v>78842</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -896,47 +896,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>454893</v>
+        <v>454951</v>
       </c>
       <c r="R4" t="n">
-        <v>6791627</v>
+        <v>6791471</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -995,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124466711</v>
+        <v>124466759</v>
       </c>
       <c r="B5" t="n">
-        <v>78842</v>
+        <v>98101</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1007,38 +998,47 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>454951</v>
+        <v>454956</v>
       </c>
       <c r="R5" t="n">
-        <v>6791471</v>
+        <v>6791469</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1097,10 +1097,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124466766</v>
+        <v>124466712</v>
       </c>
       <c r="B6" t="n">
-        <v>78810</v>
+        <v>78842</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1113,21 +1113,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1137,10 +1137,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>454930</v>
+        <v>454964</v>
       </c>
       <c r="R6" t="n">
-        <v>6791516</v>
+        <v>6791409</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1199,7 +1199,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124466768</v>
+        <v>124466779</v>
       </c>
       <c r="B7" t="n">
         <v>78810</v>
@@ -1239,10 +1239,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>454929</v>
+        <v>454886</v>
       </c>
       <c r="R7" t="n">
-        <v>6791494</v>
+        <v>6791653</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1301,7 +1301,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124466782</v>
+        <v>124466766</v>
       </c>
       <c r="B8" t="n">
         <v>78810</v>
@@ -1341,10 +1341,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>454914</v>
+        <v>454930</v>
       </c>
       <c r="R8" t="n">
-        <v>6791574</v>
+        <v>6791516</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1403,10 +1403,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124466712</v>
+        <v>124466768</v>
       </c>
       <c r="B9" t="n">
-        <v>78842</v>
+        <v>78810</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1419,21 +1419,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1443,10 +1443,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>454964</v>
+        <v>454929</v>
       </c>
       <c r="R9" t="n">
-        <v>6791409</v>
+        <v>6791494</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1505,10 +1505,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124466759</v>
+        <v>124466767</v>
       </c>
       <c r="B10" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1517,47 +1517,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>454956</v>
+        <v>454933</v>
       </c>
       <c r="R10" t="n">
-        <v>6791469</v>
+        <v>6791499</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1718,10 +1709,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124466729</v>
+        <v>124466710</v>
       </c>
       <c r="B12" t="n">
-        <v>91012</v>
+        <v>78842</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1734,21 +1725,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>185</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1758,10 +1749,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>454901</v>
+        <v>454946</v>
       </c>
       <c r="R12" t="n">
-        <v>6791638</v>
+        <v>6791477</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1820,10 +1811,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124466710</v>
+        <v>124466782</v>
       </c>
       <c r="B13" t="n">
-        <v>78842</v>
+        <v>78810</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1836,21 +1827,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1860,10 +1851,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>454946</v>
+        <v>454914</v>
       </c>
       <c r="R13" t="n">
-        <v>6791477</v>
+        <v>6791574</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1922,10 +1913,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124466783</v>
+        <v>124466729</v>
       </c>
       <c r="B14" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1938,21 +1929,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1962,10 +1953,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>454911</v>
+        <v>454901</v>
       </c>
       <c r="R14" t="n">
-        <v>6791571</v>
+        <v>6791638</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2024,10 +2015,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124466767</v>
+        <v>124466762</v>
       </c>
       <c r="B15" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2036,38 +2027,47 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>454933</v>
+        <v>454907</v>
       </c>
       <c r="R15" t="n">
-        <v>6791499</v>
+        <v>6791625</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2126,10 +2126,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124466779</v>
+        <v>124466750</v>
       </c>
       <c r="B16" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2138,38 +2138,47 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>454886</v>
+        <v>454893</v>
       </c>
       <c r="R16" t="n">
-        <v>6791653</v>
+        <v>6791627</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2228,10 +2237,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124466762</v>
+        <v>124466783</v>
       </c>
       <c r="B17" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2240,47 +2249,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Djupskär, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>454907</v>
+        <v>454911</v>
       </c>
       <c r="R17" t="n">
-        <v>6791625</v>
+        <v>6791571</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>

--- a/artfynd/A 10282-2024 artfynd.xlsx
+++ b/artfynd/A 10282-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY25"/>
+  <dimension ref="A1:AZ25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124466710</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124466711</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124466712</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124466725</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124466727</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124466729</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124466714</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124466715</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1550,6 +1595,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124160346</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1647,6 +1697,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124466766</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1744,6 +1799,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124466767</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1841,6 +1901,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124466768</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1938,6 +2003,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124466769</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2035,6 +2105,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124466778</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2132,6 +2207,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124466779</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2229,6 +2309,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124466780</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2326,6 +2411,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124466781</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2423,6 +2513,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124466782</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2520,6 +2615,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124466783</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2622,6 +2722,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124466784</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2728,6 +2833,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124466747</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2834,6 +2944,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124466750</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2940,6 +3055,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124466759</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3046,8 +3166,39 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124466762</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>